--- a/synthetic/output/doctors/doctors.xlsx
+++ b/synthetic/output/doctors/doctors.xlsx
@@ -419,12 +419,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>dr code</t>
+          <t>doctor code</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>doctor name</t>
+          <t>dr name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -439,7 +439,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>active status</t>
+          <t>doctor status</t>
         </is>
       </c>
     </row>
@@ -451,17 +451,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dr Nandini Loyal</t>
+          <t>Dr Mohini Pathak</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>T005</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>Dermatology</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dr Siddharth Murty</t>
+          <t>Dr Lakshit Upadhyay</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -488,7 +488,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -505,17 +505,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dr Xalak Randhawa</t>
+          <t>Dr Gavin Batta</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T019</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Gastroenterology</t>
+          <t>Dermatology</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -532,17 +532,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dr Luke Lanka</t>
+          <t>Dr Michael Dutta</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T019</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gastroenterology</t>
+          <t>General Medicine</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -559,17 +559,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dr Yatin Yohannan</t>
+          <t>Dr Devansh Rajan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T012</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dr Priya Rastogi</t>
+          <t>Dr Upadhriti Wadhwa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T005</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -613,17 +613,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dr Theodore Devi</t>
+          <t>Dr Advay Contractor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>Dermatology</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dr Gavin Batta</t>
+          <t>Dr Harini Choudhury</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T004</t>
+          <t>T017</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -667,17 +667,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dr Michael Dutta</t>
+          <t>Dr Radhika Dugar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T006</t>
+          <t>T017</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Gastroenterology</t>
+          <t>General Medicine</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -694,17 +694,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dr Devansh Rajan</t>
+          <t>Dr Aarush Lall</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T020</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>General Medicine</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">

--- a/synthetic/output/doctors/doctors.xlsx
+++ b/synthetic/output/doctors/doctors.xlsx
@@ -419,12 +419,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>doctor code</t>
+          <t>doctor id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>dr name</t>
+          <t>physician name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -439,7 +439,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>doctor status</t>
+          <t>status</t>
         </is>
       </c>
     </row>
@@ -451,17 +451,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dr Mohini Pathak</t>
+          <t>Dr Qadim Mallick</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>T015</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>Pulmonology</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -478,17 +478,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dr Lakshit Upadhyay</t>
+          <t>Dr Zaid Borra</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -505,17 +505,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dr Gavin Batta</t>
+          <t>Dr Guneet Bedi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T004</t>
+          <t>T018</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>Orthopedics</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -532,17 +532,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dr Michael Dutta</t>
+          <t>Dr Girik Khalsa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T011</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>General Medicine</t>
+          <t>Diabetology</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -559,17 +559,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dr Devansh Rajan</t>
+          <t>Dr Niharika Sunder</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T047</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Gastroenterology</t>
+          <t>Orthopedics</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dr Upadhriti Wadhwa</t>
+          <t>Dr Tanay Rattan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T006</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -613,17 +613,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dr Advay Contractor</t>
+          <t>Dr Nitesh Raghavan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T027</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -640,17 +640,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dr Harini Choudhury</t>
+          <t>Dr Madhavi Lanka</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T017</t>
+          <t>T007</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Diabetology</t>
+          <t>General Medicine</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -667,17 +667,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dr Radhika Dugar</t>
+          <t>Dr Bhavika Sampath</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T017</t>
+          <t>T043</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>General Medicine</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -694,17 +694,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dr Aarush Lall</t>
+          <t>Dr Mohammed Gupta</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T023</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
